--- a/data-raw/desc_subfuncao.xlsx
+++ b/data-raw/desc_subfuncao.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29301"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\2.Programação e Normas\2023\PPAG 2023 e LOA 2023\Tabelas de Apoio - geração dos volumes 2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1569275\CAMG\Splor Geral - @dcppn\00- DCPPN 2027\PPAG e LOA 2027\Dados para Volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_EC26C91BF040C27A188F7B201667BB70E4AC1C1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="3645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="3645"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$B$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$B$114</definedName>
     <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -24,12 +23,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="119">
   <si>
     <t>codigo</t>
   </si>
@@ -365,13 +375,34 @@
   </si>
   <si>
     <t>RESERVA DE CONTINGÊNCIA</t>
+  </si>
+  <si>
+    <t>COD_SUBFUNCAO</t>
+  </si>
+  <si>
+    <t>DESCRICAO</t>
+  </si>
+  <si>
+    <t>ASSISTÊNCIA À PESSOA IDOSA</t>
+  </si>
+  <si>
+    <t>ASSISTÊNCIA À PESSOA COM DEFICIÊNCIA</t>
+  </si>
+  <si>
+    <t>SERVIÇOS SOCIOASSISTENCIAIS</t>
+  </si>
+  <si>
+    <t>SEGURANÇA DE RENDA</t>
+  </si>
+  <si>
+    <t>PROMOÇÃO DA PRODUÇÃO ANIMAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -380,12 +411,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -400,8 +437,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -681,900 +719,2501 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B111"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F114"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>31</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <f>IF(A2=C2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <f>IF(B2=D2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>32</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E66" si="0">IF(A3=C3,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F66" si="1">IF(B3=D3,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>61</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>62</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="C5">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>91</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6">
+        <v>91</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>92</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7">
+        <v>92</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>121</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="C8">
+        <v>121</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <f t="shared" ref="E8:E71" si="2">IF(A8=C8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <f t="shared" ref="F8:F71" si="3">IF(B8=D8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>122</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="C9">
+        <v>122</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>123</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="C10">
+        <v>123</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>124</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="C11">
+        <v>124</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>125</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="C12">
+        <v>125</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>126</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="C13">
+        <v>126</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>127</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="C14">
+        <v>127</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>128</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
+      <c r="C15">
+        <v>128</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>129</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16">
+        <v>129</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>130</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17">
+        <v>130</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>131</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18">
+        <v>131</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>151</v>
       </c>
       <c r="B19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="C19">
+        <v>151</v>
+      </c>
+      <c r="D19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>152</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20">
+        <v>152</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>153</v>
       </c>
       <c r="B21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21">
+        <v>153</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>181</v>
       </c>
       <c r="B22" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
+      <c r="C22">
+        <v>181</v>
+      </c>
+      <c r="D22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>182</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="C23">
+        <v>182</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>183</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="C24">
+        <v>183</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>211</v>
       </c>
       <c r="B25" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
+      <c r="C25">
+        <v>211</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>212</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
+      <c r="C26">
+        <v>212</v>
+      </c>
+      <c r="D26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>241</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="C27">
+        <v>241</v>
+      </c>
+      <c r="D27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>242</v>
       </c>
       <c r="B28" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
+      <c r="C28">
+        <v>242</v>
+      </c>
+      <c r="D28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>243</v>
       </c>
       <c r="B29" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
+      <c r="C29">
+        <v>243</v>
+      </c>
+      <c r="D29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>244</v>
       </c>
       <c r="B30" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31">
+      <c r="C30">
+        <v>244</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1">
+        <v>245</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1">
+        <v>246</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>271</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
+      <c r="C33">
+        <v>271</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>272</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B34" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
+      <c r="C34">
+        <v>272</v>
+      </c>
+      <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>273</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B35" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
+      <c r="C35">
+        <v>273</v>
+      </c>
+      <c r="D35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>274</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
+      <c r="C36">
+        <v>274</v>
+      </c>
+      <c r="D36" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>301</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B37" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
+      <c r="C37">
+        <v>301</v>
+      </c>
+      <c r="D37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>302</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B38" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
+      <c r="C38">
+        <v>302</v>
+      </c>
+      <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39">
         <v>303</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B39" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
+      <c r="C39">
+        <v>303</v>
+      </c>
+      <c r="D39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>304</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B40" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
+      <c r="C40">
+        <v>304</v>
+      </c>
+      <c r="D40" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>305</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B41" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
+      <c r="C41">
+        <v>305</v>
+      </c>
+      <c r="D41" t="s">
+        <v>39</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>306</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B42" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
+      <c r="C42">
+        <v>306</v>
+      </c>
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>331</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B43" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
+      <c r="C43">
+        <v>331</v>
+      </c>
+      <c r="D43" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>332</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B44" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
+      <c r="C44">
+        <v>332</v>
+      </c>
+      <c r="D44" t="s">
+        <v>42</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>333</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B45" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
+      <c r="C45">
+        <v>333</v>
+      </c>
+      <c r="D45" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>334</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B46" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
+      <c r="C46">
+        <v>334</v>
+      </c>
+      <c r="D46" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47">
         <v>361</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B47" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
+      <c r="C47">
+        <v>361</v>
+      </c>
+      <c r="D47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48">
         <v>362</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B48" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
+      <c r="C48">
+        <v>362</v>
+      </c>
+      <c r="D48" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49">
         <v>363</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B49" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
+      <c r="C49">
+        <v>363</v>
+      </c>
+      <c r="D49" t="s">
+        <v>47</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50">
         <v>364</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B50" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
+      <c r="C50">
+        <v>364</v>
+      </c>
+      <c r="D50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51">
         <v>365</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B51" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
+      <c r="C51">
+        <v>365</v>
+      </c>
+      <c r="D51" t="s">
+        <v>49</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52">
         <v>366</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B52" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
+      <c r="C52">
+        <v>366</v>
+      </c>
+      <c r="D52" t="s">
+        <v>50</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53">
         <v>367</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B53" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
+      <c r="C53">
+        <v>367</v>
+      </c>
+      <c r="D53" t="s">
+        <v>51</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54">
         <v>368</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B54" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
+      <c r="C54">
+        <v>368</v>
+      </c>
+      <c r="D54" t="s">
+        <v>52</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55">
         <v>391</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B55" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54">
+      <c r="C55">
+        <v>391</v>
+      </c>
+      <c r="D55" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56">
         <v>392</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B56" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55">
+      <c r="C56">
+        <v>392</v>
+      </c>
+      <c r="D56" t="s">
+        <v>54</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57">
         <v>421</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B57" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56">
+      <c r="C57">
+        <v>421</v>
+      </c>
+      <c r="D57" t="s">
+        <v>55</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58">
         <v>422</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B58" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57">
+      <c r="C58">
+        <v>422</v>
+      </c>
+      <c r="D58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59">
         <v>423</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B59" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58">
+      <c r="C59">
+        <v>423</v>
+      </c>
+      <c r="D59" t="s">
+        <v>57</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60">
         <v>451</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B60" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59">
+      <c r="C60">
+        <v>451</v>
+      </c>
+      <c r="D60" t="s">
+        <v>58</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61">
         <v>452</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B61" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60">
+      <c r="C61">
+        <v>452</v>
+      </c>
+      <c r="D61" t="s">
+        <v>59</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62">
         <v>453</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B62" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61">
+      <c r="C62">
+        <v>453</v>
+      </c>
+      <c r="D62" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63">
         <v>481</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B63" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62">
+      <c r="C63">
+        <v>481</v>
+      </c>
+      <c r="D63" t="s">
+        <v>61</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64">
         <v>482</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B64" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63">
+      <c r="C64">
+        <v>482</v>
+      </c>
+      <c r="D64" t="s">
+        <v>62</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65">
         <v>511</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B65" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64">
+      <c r="C65">
+        <v>511</v>
+      </c>
+      <c r="D65" t="s">
+        <v>63</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66">
         <v>512</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B66" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65">
+      <c r="C66">
+        <v>512</v>
+      </c>
+      <c r="D66" t="s">
+        <v>64</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67">
         <v>541</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B67" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66">
+      <c r="C67">
+        <v>541</v>
+      </c>
+      <c r="D67" t="s">
+        <v>65</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68">
         <v>542</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B68" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67">
+      <c r="C68">
+        <v>542</v>
+      </c>
+      <c r="D68" t="s">
+        <v>66</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69">
         <v>543</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B69" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68">
+      <c r="C69">
+        <v>543</v>
+      </c>
+      <c r="D69" t="s">
+        <v>67</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70">
         <v>544</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B70" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69">
+      <c r="C70">
+        <v>544</v>
+      </c>
+      <c r="D70" t="s">
+        <v>68</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71">
         <v>545</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B71" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70">
+      <c r="C71">
+        <v>545</v>
+      </c>
+      <c r="D71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72">
         <v>571</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B72" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71">
+      <c r="C72">
+        <v>571</v>
+      </c>
+      <c r="D72" t="s">
+        <v>70</v>
+      </c>
+      <c r="E72">
+        <f t="shared" ref="E72:E114" si="4">IF(A72=C72,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ref="F72:F114" si="5">IF(B72=D72,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73">
         <v>572</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B73" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72">
+      <c r="C73">
+        <v>572</v>
+      </c>
+      <c r="D73" t="s">
+        <v>71</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74">
         <v>573</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B74" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73">
+      <c r="C74">
+        <v>573</v>
+      </c>
+      <c r="D74" t="s">
+        <v>72</v>
+      </c>
+      <c r="E74">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1">
+        <v>602</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E75" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F75" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76">
         <v>605</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B76" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74">
+      <c r="C76">
+        <v>605</v>
+      </c>
+      <c r="D76" t="s">
+        <v>73</v>
+      </c>
+      <c r="E76">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77">
         <v>606</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B77" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75">
+      <c r="C77">
+        <v>606</v>
+      </c>
+      <c r="D77" t="s">
+        <v>74</v>
+      </c>
+      <c r="E77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78">
         <v>607</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B78" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76">
+      <c r="C78">
+        <v>607</v>
+      </c>
+      <c r="D78" t="s">
+        <v>75</v>
+      </c>
+      <c r="E78">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79">
         <v>608</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B79" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77">
+      <c r="C79">
+        <v>608</v>
+      </c>
+      <c r="D79" t="s">
+        <v>76</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80">
         <v>609</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B80" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78">
+      <c r="C80">
+        <v>609</v>
+      </c>
+      <c r="D80" t="s">
+        <v>77</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81">
         <v>631</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B81" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79">
+      <c r="C81">
+        <v>631</v>
+      </c>
+      <c r="D81" t="s">
+        <v>78</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82">
         <v>632</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B82" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80">
+      <c r="C82">
+        <v>632</v>
+      </c>
+      <c r="D82" t="s">
+        <v>79</v>
+      </c>
+      <c r="E82">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83">
         <v>661</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B83" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81">
+      <c r="C83">
+        <v>661</v>
+      </c>
+      <c r="D83" t="s">
+        <v>80</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84">
         <v>662</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B84" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82">
+      <c r="C84">
+        <v>662</v>
+      </c>
+      <c r="D84" t="s">
+        <v>81</v>
+      </c>
+      <c r="E84">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85">
         <v>663</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B85" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83">
+      <c r="C85">
+        <v>663</v>
+      </c>
+      <c r="D85" t="s">
+        <v>82</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86">
         <v>664</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B86" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84">
+      <c r="C86">
+        <v>664</v>
+      </c>
+      <c r="D86" t="s">
+        <v>83</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87">
         <v>665</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B87" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85">
+      <c r="C87">
+        <v>665</v>
+      </c>
+      <c r="D87" t="s">
+        <v>84</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88">
         <v>691</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B88" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86">
+      <c r="C88">
+        <v>691</v>
+      </c>
+      <c r="D88" t="s">
+        <v>85</v>
+      </c>
+      <c r="E88">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89">
         <v>692</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B89" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87">
+      <c r="C89">
+        <v>692</v>
+      </c>
+      <c r="D89" t="s">
+        <v>86</v>
+      </c>
+      <c r="E89">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90">
         <v>693</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B90" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88">
+      <c r="C90">
+        <v>693</v>
+      </c>
+      <c r="D90" t="s">
+        <v>87</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91">
         <v>694</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B91" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89">
+      <c r="C91">
+        <v>694</v>
+      </c>
+      <c r="D91" t="s">
+        <v>88</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92">
         <v>695</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B92" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90">
+      <c r="C92">
+        <v>695</v>
+      </c>
+      <c r="D92" t="s">
+        <v>89</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93">
         <v>721</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B93" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91">
+      <c r="C93">
+        <v>721</v>
+      </c>
+      <c r="D93" t="s">
+        <v>90</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94">
         <v>722</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B94" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92">
+      <c r="C94">
+        <v>722</v>
+      </c>
+      <c r="D94" t="s">
+        <v>91</v>
+      </c>
+      <c r="E94">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95">
         <v>751</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B95" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93">
+      <c r="C95">
+        <v>751</v>
+      </c>
+      <c r="D95" t="s">
+        <v>92</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96">
         <v>752</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B96" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94">
+      <c r="C96">
+        <v>752</v>
+      </c>
+      <c r="D96" t="s">
+        <v>93</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97">
         <v>753</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B97" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95">
+      <c r="C97">
+        <v>753</v>
+      </c>
+      <c r="D97" t="s">
+        <v>94</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F97">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98">
         <v>754</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B98" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96">
+      <c r="C98">
+        <v>754</v>
+      </c>
+      <c r="D98" t="s">
+        <v>95</v>
+      </c>
+      <c r="E98">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99">
         <v>781</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B99" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97">
+      <c r="C99">
+        <v>781</v>
+      </c>
+      <c r="D99" t="s">
+        <v>96</v>
+      </c>
+      <c r="E99">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F99">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100">
         <v>782</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B100" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98">
+      <c r="C100">
+        <v>782</v>
+      </c>
+      <c r="D100" t="s">
+        <v>97</v>
+      </c>
+      <c r="E100">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F100">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101">
         <v>783</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B101" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99">
+      <c r="C101">
+        <v>783</v>
+      </c>
+      <c r="D101" t="s">
+        <v>98</v>
+      </c>
+      <c r="E101">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F101">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102">
         <v>784</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B102" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100">
+      <c r="C102">
+        <v>784</v>
+      </c>
+      <c r="D102" t="s">
+        <v>99</v>
+      </c>
+      <c r="E102">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F102">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103">
         <v>785</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B103" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101">
+      <c r="C103">
+        <v>785</v>
+      </c>
+      <c r="D103" t="s">
+        <v>100</v>
+      </c>
+      <c r="E103">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F103">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104">
         <v>811</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B104" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102">
+      <c r="C104">
+        <v>811</v>
+      </c>
+      <c r="D104" t="s">
+        <v>101</v>
+      </c>
+      <c r="E104">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105">
         <v>812</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B105" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103">
+      <c r="C105">
+        <v>812</v>
+      </c>
+      <c r="D105" t="s">
+        <v>102</v>
+      </c>
+      <c r="E105">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F105">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106">
         <v>813</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B106" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104">
+      <c r="C106">
+        <v>813</v>
+      </c>
+      <c r="D106" t="s">
+        <v>103</v>
+      </c>
+      <c r="E106">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F106">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107">
         <v>841</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B107" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105">
+      <c r="C107">
+        <v>841</v>
+      </c>
+      <c r="D107" t="s">
+        <v>104</v>
+      </c>
+      <c r="E107">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F107">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108">
         <v>842</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B108" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106">
+      <c r="C108">
+        <v>842</v>
+      </c>
+      <c r="D108" t="s">
+        <v>105</v>
+      </c>
+      <c r="E108">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F108">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109">
         <v>843</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B109" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107">
+      <c r="C109">
+        <v>843</v>
+      </c>
+      <c r="D109" t="s">
+        <v>106</v>
+      </c>
+      <c r="E109">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F109">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110">
         <v>844</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B110" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108">
+      <c r="C110">
+        <v>844</v>
+      </c>
+      <c r="D110" t="s">
+        <v>107</v>
+      </c>
+      <c r="E110">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F110">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111">
         <v>845</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B111" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109">
+      <c r="C111">
+        <v>845</v>
+      </c>
+      <c r="D111" t="s">
+        <v>108</v>
+      </c>
+      <c r="E111">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F111">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112">
         <v>846</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B112" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110">
+      <c r="C112">
+        <v>846</v>
+      </c>
+      <c r="D112" t="s">
+        <v>109</v>
+      </c>
+      <c r="E112">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F112">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113">
         <v>847</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B113" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111">
+      <c r="C113">
+        <v>847</v>
+      </c>
+      <c r="D113" t="s">
+        <v>110</v>
+      </c>
+      <c r="E113">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F113">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114">
         <v>999</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B114" t="s">
         <v>111</v>
+      </c>
+      <c r="C114">
+        <v>999</v>
+      </c>
+      <c r="D114" t="s">
+        <v>111</v>
+      </c>
+      <c r="E114">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F114">
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1584,24 +3223,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1610,9 +3231,9 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -1871,14 +3492,64 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A8736FE-6255-4FD1-8C32-47721AF24FF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EAA5A96-60E0-4C51-8584-699CBD88CF93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EAA5A96-60E0-4C51-8584-699CBD88CF93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F771552-5651-4207-9E9D-C4823C65627F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60504B4E-13D0-4AB7-834B-C4A00410F540}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A8736FE-6255-4FD1-8C32-47721AF24FF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data-raw/desc_subfuncao.xlsx
+++ b/data-raw/desc_subfuncao.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29301"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\2.Programação e Normas\2023\PPAG 2023 e LOA 2023\Tabelas de Apoio - geração dos volumes 2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x1569275\CAMG\Splor Geral - @dcppn\00- DCPPN 2027\PPAG e LOA 2027\Dados para Volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_EC26C91BF040C27A188F7B201667BB70E4AC1C1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="3645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="3645"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -24,6 +23,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -370,8 +380,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -681,15 +691,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B111"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="53.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>31</v>
       </c>
@@ -705,7 +715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>32</v>
       </c>
@@ -713,7 +723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>61</v>
       </c>
@@ -721,7 +731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>62</v>
       </c>
@@ -729,7 +739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>91</v>
       </c>
@@ -737,7 +747,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>92</v>
       </c>
@@ -745,7 +755,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>121</v>
       </c>
@@ -753,7 +763,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>122</v>
       </c>
@@ -761,7 +771,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>123</v>
       </c>
@@ -769,7 +779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>124</v>
       </c>
@@ -777,7 +787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>125</v>
       </c>
@@ -785,7 +795,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>126</v>
       </c>
@@ -793,7 +803,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>127</v>
       </c>
@@ -801,7 +811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>128</v>
       </c>
@@ -809,7 +819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>129</v>
       </c>
@@ -817,7 +827,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>130</v>
       </c>
@@ -825,7 +835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>131</v>
       </c>
@@ -833,7 +843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>151</v>
       </c>
@@ -841,7 +851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>152</v>
       </c>
@@ -849,7 +859,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>153</v>
       </c>
@@ -857,7 +867,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>181</v>
       </c>
@@ -865,7 +875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>182</v>
       </c>
@@ -873,7 +883,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>183</v>
       </c>
@@ -881,7 +891,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>211</v>
       </c>
@@ -889,7 +899,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>212</v>
       </c>
@@ -897,7 +907,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>241</v>
       </c>
@@ -905,7 +915,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>242</v>
       </c>
@@ -913,7 +923,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>243</v>
       </c>
@@ -921,7 +931,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>244</v>
       </c>
@@ -929,7 +939,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>271</v>
       </c>
@@ -937,7 +947,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>272</v>
       </c>
@@ -945,7 +955,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>273</v>
       </c>
@@ -953,7 +963,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>274</v>
       </c>
@@ -961,7 +971,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>301</v>
       </c>
@@ -969,7 +979,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>302</v>
       </c>
@@ -977,7 +987,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>303</v>
       </c>
@@ -985,7 +995,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>304</v>
       </c>
@@ -993,7 +1003,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>305</v>
       </c>
@@ -1001,7 +1011,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>306</v>
       </c>
@@ -1009,7 +1019,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>331</v>
       </c>
@@ -1017,7 +1027,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>332</v>
       </c>
@@ -1025,7 +1035,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>333</v>
       </c>
@@ -1033,7 +1043,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>334</v>
       </c>
@@ -1041,7 +1051,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>361</v>
       </c>
@@ -1049,7 +1059,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>362</v>
       </c>
@@ -1057,7 +1067,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>363</v>
       </c>
@@ -1065,7 +1075,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>364</v>
       </c>
@@ -1073,7 +1083,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>365</v>
       </c>
@@ -1081,7 +1091,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>366</v>
       </c>
@@ -1089,7 +1099,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>367</v>
       </c>
@@ -1097,7 +1107,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>368</v>
       </c>
@@ -1105,7 +1115,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>391</v>
       </c>
@@ -1113,7 +1123,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>392</v>
       </c>
@@ -1121,7 +1131,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>421</v>
       </c>
@@ -1129,7 +1139,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>422</v>
       </c>
@@ -1137,7 +1147,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>423</v>
       </c>
@@ -1145,7 +1155,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>451</v>
       </c>
@@ -1153,7 +1163,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>452</v>
       </c>
@@ -1161,7 +1171,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>453</v>
       </c>
@@ -1169,7 +1179,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>481</v>
       </c>
@@ -1177,7 +1187,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>482</v>
       </c>
@@ -1185,7 +1195,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>511</v>
       </c>
@@ -1193,7 +1203,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>512</v>
       </c>
@@ -1201,7 +1211,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>541</v>
       </c>
@@ -1209,7 +1219,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>542</v>
       </c>
@@ -1217,7 +1227,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>543</v>
       </c>
@@ -1225,7 +1235,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>544</v>
       </c>
@@ -1233,7 +1243,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>545</v>
       </c>
@@ -1241,7 +1251,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>571</v>
       </c>
@@ -1249,7 +1259,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>572</v>
       </c>
@@ -1257,7 +1267,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>573</v>
       </c>
@@ -1265,7 +1275,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>605</v>
       </c>
@@ -1273,7 +1283,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>606</v>
       </c>
@@ -1281,7 +1291,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>607</v>
       </c>
@@ -1289,7 +1299,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>608</v>
       </c>
@@ -1297,7 +1307,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>609</v>
       </c>
@@ -1305,7 +1315,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>631</v>
       </c>
@@ -1313,7 +1323,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>632</v>
       </c>
@@ -1321,7 +1331,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>661</v>
       </c>
@@ -1329,7 +1339,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>662</v>
       </c>
@@ -1337,7 +1347,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>663</v>
       </c>
@@ -1345,7 +1355,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>664</v>
       </c>
@@ -1353,7 +1363,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>665</v>
       </c>
@@ -1361,7 +1371,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>691</v>
       </c>
@@ -1369,7 +1379,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>692</v>
       </c>
@@ -1377,7 +1387,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>693</v>
       </c>
@@ -1385,7 +1395,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>694</v>
       </c>
@@ -1393,7 +1403,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>695</v>
       </c>
@@ -1401,7 +1411,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>721</v>
       </c>
@@ -1409,7 +1419,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>722</v>
       </c>
@@ -1417,7 +1427,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>751</v>
       </c>
@@ -1425,7 +1435,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>752</v>
       </c>
@@ -1433,7 +1443,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>753</v>
       </c>
@@ -1441,7 +1451,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>754</v>
       </c>
@@ -1449,7 +1459,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>781</v>
       </c>
@@ -1457,7 +1467,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>782</v>
       </c>
@@ -1465,7 +1475,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>783</v>
       </c>
@@ -1473,7 +1483,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>784</v>
       </c>
@@ -1481,7 +1491,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>785</v>
       </c>
@@ -1489,7 +1499,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>811</v>
       </c>
@@ -1497,7 +1507,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>812</v>
       </c>
@@ -1505,7 +1515,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>813</v>
       </c>
@@ -1513,7 +1523,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>841</v>
       </c>
@@ -1521,7 +1531,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>842</v>
       </c>
@@ -1529,7 +1539,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>843</v>
       </c>
@@ -1537,7 +1547,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>844</v>
       </c>
@@ -1545,7 +1555,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>845</v>
       </c>
@@ -1553,7 +1563,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>846</v>
       </c>
@@ -1561,7 +1571,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>847</v>
       </c>
@@ -1569,7 +1579,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>999</v>
       </c>
@@ -1584,6 +1594,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
@@ -1601,18 +1620,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="b1e0f6055e0e9a4b9e75d6c71ee7de91">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b43930f3490e4d4da1ab3f8da7df6f51" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -1872,13 +1882,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A8736FE-6255-4FD1-8C32-47721AF24FF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EAA5A96-60E0-4C51-8584-699CBD88CF93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EAA5A96-60E0-4C51-8584-699CBD88CF93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A8736FE-6255-4FD1-8C32-47721AF24FF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60504B4E-13D0-4AB7-834B-C4A00410F540}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F771552-5651-4207-9E9D-C4823C65627F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6f4338ef-addb-4c87-aefe-1895241b335f"/>
+    <ds:schemaRef ds:uri="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>